--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20211.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="29">
   <si>
     <t>Mat</t>
   </si>
@@ -79,100 +79,31 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>GARCIA</t>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>SAN JUAN</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>NIEVES</t>
   </si>
   <si>
     <t>AGUILAR</t>
   </si>
   <si>
-    <t>ESPINOSA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>SAN JUAN</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>VIVAS</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>VALIENTE</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>SALVADOR</t>
-  </si>
-  <si>
-    <t>CRISTIAN JAHIR</t>
-  </si>
-  <si>
     <t>OSVALDO</t>
   </si>
   <si>
-    <t>GERARDO RAUL</t>
-  </si>
-  <si>
-    <t>CRISTHIAN</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>SAUL</t>
-  </si>
-  <si>
-    <t>YAHIR</t>
+    <t>CANDIDO</t>
   </si>
   <si>
     <t>ANGEL FIDEL</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>CHRISTOFER</t>
-  </si>
-  <si>
-    <t>YAIR</t>
   </si>
 </sst>
 </file>
@@ -573,19 +504,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>44.12</v>
+        <v>79.41</v>
       </c>
       <c r="H2">
-        <v>9.5</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -599,19 +530,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G3">
-        <v>57.58</v>
+        <v>66.67</v>
       </c>
       <c r="H3">
-        <v>8.300000000000001</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -625,19 +556,19 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G4">
-        <v>69.56999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -690,16 +621,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E2">
         <v>15</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>55.88</v>
+      </c>
+      <c r="H2">
+        <v>9.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -713,16 +647,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>36.36</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -736,16 +673,19 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E4">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>52.17</v>
+      </c>
+      <c r="H4">
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -798,19 +738,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>44.12</v>
+        <v>79.41</v>
       </c>
       <c r="H2">
-        <v>9.5</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -824,19 +764,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>57.58</v>
+        <v>72.73</v>
       </c>
       <c r="H3">
-        <v>8.300000000000001</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -850,19 +790,19 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G4">
-        <v>69.56999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -872,7 +812,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -904,278 +844,71 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920168</v>
+        <v>20330051920070</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920081</v>
+        <v>21330051920176</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920070</v>
+        <v>21330051920177</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>19330051920055</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920153</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920157</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920161</v>
-      </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" t="s">
-        <v>46</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920171</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920177</v>
-      </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" t="s">
-        <v>48</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920178</v>
-      </c>
-      <c r="B11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920182</v>
-      </c>
-      <c r="B12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920066</v>
-      </c>
-      <c r="B13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" t="s">
-        <v>51</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20211.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20211.xlsx
@@ -79,7 +79,7 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
+    <t>VIVAS</t>
   </si>
   <si>
     <t>RUIZ</t>
@@ -88,7 +88,7 @@
     <t>SAN JUAN</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
+    <t>TLAXCALA</t>
   </si>
   <si>
     <t>NIEVES</t>
@@ -97,7 +97,7 @@
     <t>AGUILAR</t>
   </si>
   <si>
-    <t>OSVALDO</t>
+    <t>MARIA JOSE</t>
   </si>
   <si>
     <t>CANDIDO</t>
@@ -844,7 +844,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920070</v>
+        <v>21330051920183</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
@@ -856,13 +856,13 @@
         <v>26</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -885,7 +885,7 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -908,7 +908,7 @@
         <v>11</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20211.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20211.xlsx
@@ -885,7 +885,7 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">

--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20211.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20211.xlsx
@@ -79,31 +79,31 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>VIVAS</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>SAN JUAN</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>CANDIDO</t>
-  </si>
-  <si>
-    <t>ANGEL FIDEL</t>
+    <t>EVANGELISTA</t>
+  </si>
+  <si>
+    <t>LOYO</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>JUAN GERARDO</t>
+  </si>
+  <si>
+    <t>DIEGO ARMANDO</t>
+  </si>
+  <si>
+    <t>NORKYS AIRY</t>
   </si>
 </sst>
 </file>
@@ -621,19 +621,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>55.88</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H2">
-        <v>9.1</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -647,19 +647,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>36.36</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -673,19 +673,19 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="G4">
-        <v>52.17</v>
+        <v>91.3</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -741,16 +741,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>79.41</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H2">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -776,7 +776,7 @@
         <v>72.73</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -793,16 +793,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G4">
-        <v>82.61</v>
+        <v>91.3</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -844,7 +844,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920183</v>
+        <v>21330051920156</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
@@ -862,12 +862,12 @@
         <v>11</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920176</v>
+        <v>21330051920164</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
@@ -885,12 +885,12 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920177</v>
+        <v>20330051920074</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
@@ -902,13 +902,13 @@
         <v>28</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
